--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125798418</v>
       </c>
       <c r="B2" t="n">
-        <v>56581</v>
+        <v>56582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125798418</v>
       </c>
       <c r="B2" t="n">
-        <v>56582</v>
+        <v>56586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125798418</v>
       </c>
       <c r="B2" t="n">
-        <v>56586</v>
+        <v>56587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,127 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128820366</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57729</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fridhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>560709</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6282821</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sankt Sigfrid</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Angelica  Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Angelica  Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128820366</v>
       </c>
       <c r="B3" t="n">
-        <v>57729</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128820366</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128820366</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128820366</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125798418</v>
+        <v>128820366</v>
       </c>
       <c r="B2" t="n">
-        <v>56587</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100070</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,14 +708,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128820366</v>
+        <v>125798418</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>56879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>100070</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,14 +829,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -875,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,6 +914,132 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127444919</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56879</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fridhem, Fridhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>560695</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6282808</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sankt Sigfrid</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Björn Karpestam</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Björn Karpestam</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9153-2023 artfynd.xlsx
+++ b/artfynd/A 9153-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820366</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125798418</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,8 +1055,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127444919</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>